--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaalproduct_Auto_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaalproduct_Auto_OV.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>147491</v>
+        <v>153719</v>
       </c>
       <c r="C2">
-        <v>241979</v>
+        <v>249548</v>
       </c>
       <c r="D2">
-        <v>301835</v>
+        <v>306161</v>
       </c>
       <c r="E2">
-        <v>330579</v>
+        <v>333899</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>174804</v>
+        <v>187570</v>
       </c>
       <c r="C3">
-        <v>287087</v>
+        <v>298780</v>
       </c>
       <c r="D3">
-        <v>355425</v>
+        <v>360897</v>
       </c>
       <c r="E3">
-        <v>392100</v>
+        <v>396037</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>150924</v>
+        <v>154033</v>
       </c>
       <c r="C4">
-        <v>262448</v>
+        <v>265364</v>
       </c>
       <c r="D4">
-        <v>334148</v>
+        <v>335413</v>
       </c>
       <c r="E4">
-        <v>370244</v>
+        <v>370982</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>114969</v>
+        <v>123900</v>
       </c>
       <c r="C5">
-        <v>190639</v>
+        <v>200616</v>
       </c>
       <c r="D5">
-        <v>234167</v>
+        <v>238557</v>
       </c>
       <c r="E5">
-        <v>259873</v>
+        <v>262631</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>96061</v>
+        <v>104828</v>
       </c>
       <c r="C6">
-        <v>163155</v>
+        <v>170563</v>
       </c>
       <c r="D6">
-        <v>205674</v>
+        <v>209293</v>
       </c>
       <c r="E6">
-        <v>226086</v>
+        <v>228479</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>11262</v>
+        <v>11812</v>
       </c>
       <c r="C7">
-        <v>18120</v>
+        <v>18646</v>
       </c>
       <c r="D7">
-        <v>22250</v>
+        <v>22603</v>
       </c>
       <c r="E7">
-        <v>24086</v>
+        <v>24450</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>293532</v>
+        <v>421199</v>
       </c>
       <c r="C8">
-        <v>665285</v>
+        <v>796445</v>
       </c>
       <c r="D8">
-        <v>972571</v>
+        <v>1080273</v>
       </c>
       <c r="E8">
-        <v>1206415</v>
+        <v>1246708</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>137103</v>
+        <v>166225</v>
       </c>
       <c r="C9">
-        <v>231547</v>
+        <v>254628</v>
       </c>
       <c r="D9">
-        <v>292693</v>
+        <v>301995</v>
       </c>
       <c r="E9">
-        <v>324225</v>
+        <v>329883</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>69313</v>
+        <v>73039</v>
       </c>
       <c r="C10">
-        <v>108016</v>
+        <v>110624</v>
       </c>
       <c r="D10">
-        <v>131645</v>
+        <v>132774</v>
       </c>
       <c r="E10">
-        <v>141130</v>
+        <v>141830</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>12612</v>
+        <v>13282</v>
       </c>
       <c r="C11">
-        <v>18734</v>
+        <v>19101</v>
       </c>
       <c r="D11">
-        <v>22629</v>
+        <v>22783</v>
       </c>
       <c r="E11">
-        <v>26194</v>
+        <v>26312</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>28104</v>
+        <v>32805</v>
       </c>
       <c r="C12">
-        <v>47709</v>
+        <v>50220</v>
       </c>
       <c r="D12">
-        <v>59199</v>
+        <v>59808</v>
       </c>
       <c r="E12">
-        <v>62618</v>
+        <v>62952</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>37939</v>
+        <v>40013</v>
       </c>
       <c r="C13">
-        <v>59402</v>
+        <v>60642</v>
       </c>
       <c r="D13">
-        <v>73592</v>
+        <v>74156</v>
       </c>
       <c r="E13">
-        <v>79938</v>
+        <v>80322</v>
       </c>
     </row>
   </sheetData>
